--- a/D0_TShirt_2024_Material_New Launches 1.xlsx
+++ b/D0_TShirt_2024_Material_New Launches 1.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_23F921EDB3BB48B5A75710D67BF5411E5492C7A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://quantmatrixai-my.sharepoint.com/personal/saahil_kejriwal_quantmatrix_ai/Documents/Demos/price_optimisation_suite/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_23F921EDB3BB48B5A75710D67BF5411E5492C7A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2957725E-6540-443C-85F5-567CC08AF3EE}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -116,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,9 +484,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R698"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>249</v>
       </c>
@@ -593,7 +617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>249</v>
       </c>
@@ -649,7 +673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>249</v>
       </c>
@@ -705,7 +729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>249</v>
       </c>
@@ -761,7 +785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>249</v>
       </c>
@@ -817,7 +841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>249</v>
       </c>
@@ -873,7 +897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>249</v>
       </c>
@@ -929,7 +953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>249</v>
       </c>
@@ -985,7 +1009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>249</v>
       </c>
@@ -1041,7 +1065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>249</v>
       </c>
@@ -1097,7 +1121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>249</v>
       </c>
@@ -1153,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>249</v>
       </c>
@@ -1209,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>299</v>
       </c>
@@ -1265,7 +1289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>299</v>
       </c>
@@ -1321,7 +1345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>299</v>
       </c>
@@ -1377,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>299</v>
       </c>
@@ -1433,7 +1457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>299</v>
       </c>
@@ -1489,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>299</v>
       </c>
@@ -1545,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>299</v>
       </c>
@@ -1601,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>299</v>
       </c>
@@ -1657,7 +1681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>299</v>
       </c>
@@ -1713,7 +1737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>299</v>
       </c>
@@ -1769,7 +1793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>299</v>
       </c>
@@ -1825,7 +1849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>299</v>
       </c>
@@ -1881,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>299</v>
       </c>
@@ -1937,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>299</v>
       </c>
@@ -1993,7 +2017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>299</v>
       </c>
@@ -2049,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>299</v>
       </c>
@@ -2105,7 +2129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>299</v>
       </c>
@@ -2161,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>299</v>
       </c>
@@ -2217,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>299</v>
       </c>
@@ -2273,7 +2297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>299</v>
       </c>
@@ -2329,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>299</v>
       </c>
@@ -2385,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>299</v>
       </c>
@@ -2441,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>299</v>
       </c>
@@ -2497,7 +2521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>299</v>
       </c>
@@ -2553,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>299</v>
       </c>
@@ -2609,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>299</v>
       </c>
@@ -2665,7 +2689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>299</v>
       </c>
@@ -2721,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>299</v>
       </c>
@@ -2777,7 +2801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>299</v>
       </c>
@@ -2833,7 +2857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>299</v>
       </c>
@@ -2889,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>299</v>
       </c>
@@ -2945,7 +2969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>299</v>
       </c>
@@ -3001,7 +3025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>299</v>
       </c>
@@ -3057,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>299</v>
       </c>
@@ -3113,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>299</v>
       </c>
@@ -3169,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>299</v>
       </c>
@@ -3225,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>299</v>
       </c>
@@ -3281,7 +3305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>299</v>
       </c>
@@ -3337,7 +3361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>299</v>
       </c>
@@ -3393,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>299</v>
       </c>
@@ -3449,7 +3473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>299</v>
       </c>
@@ -3505,7 +3529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>299</v>
       </c>
@@ -3561,7 +3585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>299</v>
       </c>
@@ -3617,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>299</v>
       </c>
@@ -3673,7 +3697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>299</v>
       </c>
@@ -3729,7 +3753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>299</v>
       </c>
@@ -3785,7 +3809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>299</v>
       </c>
@@ -3841,7 +3865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>299</v>
       </c>
@@ -3897,7 +3921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:18">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>299</v>
       </c>
@@ -3953,7 +3977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:18">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>299</v>
       </c>
@@ -4009,7 +4033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>299</v>
       </c>
@@ -4065,7 +4089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:18">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>299</v>
       </c>
@@ -4121,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>299</v>
       </c>
@@ -4177,7 +4201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>299</v>
       </c>
@@ -4233,7 +4257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>349</v>
       </c>
@@ -4289,7 +4313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:18">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>349</v>
       </c>
@@ -4345,7 +4369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:18">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>349</v>
       </c>
@@ -4401,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:18">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>349</v>
       </c>
@@ -4457,7 +4481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>349</v>
       </c>
@@ -4513,7 +4537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>349</v>
       </c>
@@ -4569,7 +4593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>349</v>
       </c>
@@ -4625,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>349</v>
       </c>
@@ -4681,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>349</v>
       </c>
@@ -4737,7 +4761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>349</v>
       </c>
@@ -4793,7 +4817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>349</v>
       </c>
@@ -4849,7 +4873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>349</v>
       </c>
@@ -4905,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>349</v>
       </c>
@@ -4961,7 +4985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>349</v>
       </c>
@@ -5017,7 +5041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>349</v>
       </c>
@@ -5073,7 +5097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>349</v>
       </c>
@@ -5129,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>349</v>
       </c>
@@ -5185,7 +5209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>349</v>
       </c>
@@ -5241,7 +5265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>349</v>
       </c>
@@ -5297,7 +5321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>349</v>
       </c>
@@ -5353,7 +5377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>349</v>
       </c>
@@ -5409,7 +5433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>349</v>
       </c>
@@ -5465,7 +5489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>349</v>
       </c>
@@ -5521,7 +5545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>349</v>
       </c>
@@ -5577,7 +5601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>349</v>
       </c>
@@ -5633,7 +5657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>349</v>
       </c>
@@ -5689,7 +5713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>349</v>
       </c>
@@ -5745,7 +5769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>349</v>
       </c>
@@ -5801,7 +5825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>349</v>
       </c>
@@ -5857,7 +5881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>349</v>
       </c>
@@ -5913,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>349</v>
       </c>
@@ -5969,7 +5993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>349</v>
       </c>
@@ -6025,7 +6049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>349</v>
       </c>
@@ -6081,7 +6105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>399</v>
       </c>
@@ -6137,7 +6161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>399</v>
       </c>
@@ -6193,7 +6217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>399</v>
       </c>
@@ -6249,7 +6273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>399</v>
       </c>
@@ -6305,7 +6329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>399</v>
       </c>
@@ -6361,7 +6385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>399</v>
       </c>
@@ -6417,7 +6441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>399</v>
       </c>
@@ -6473,7 +6497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>399</v>
       </c>
@@ -6529,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>399</v>
       </c>
@@ -6585,7 +6609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>399</v>
       </c>
@@ -6641,7 +6665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>399</v>
       </c>
@@ -6697,7 +6721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>399</v>
       </c>
@@ -6753,7 +6777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>399</v>
       </c>
@@ -6809,7 +6833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>399</v>
       </c>
@@ -6865,7 +6889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>399</v>
       </c>
@@ -6921,7 +6945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>399</v>
       </c>
@@ -6977,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>399</v>
       </c>
@@ -7033,7 +7057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>399</v>
       </c>
@@ -7089,7 +7113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>399</v>
       </c>
@@ -7145,7 +7169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:18">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>399</v>
       </c>
@@ -7201,7 +7225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>399</v>
       </c>
@@ -7257,7 +7281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>399</v>
       </c>
@@ -7313,7 +7337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>399</v>
       </c>
@@ -7369,7 +7393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>399</v>
       </c>
@@ -7425,7 +7449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>399</v>
       </c>
@@ -7481,7 +7505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>399</v>
       </c>
@@ -7537,7 +7561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>399</v>
       </c>
@@ -7593,7 +7617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>399</v>
       </c>
@@ -7649,7 +7673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>399</v>
       </c>
@@ -7705,7 +7729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>399</v>
       </c>
@@ -7761,7 +7785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>399</v>
       </c>
@@ -7817,7 +7841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>399</v>
       </c>
@@ -7873,7 +7897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>399</v>
       </c>
@@ -7929,7 +7953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:18">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>399</v>
       </c>
@@ -7985,7 +8009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:18">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>399</v>
       </c>
@@ -8041,7 +8065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:18">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>399</v>
       </c>
@@ -8097,7 +8121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>399</v>
       </c>
@@ -8153,7 +8177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>399</v>
       </c>
@@ -8209,7 +8233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>399</v>
       </c>
@@ -8265,7 +8289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>399</v>
       </c>
@@ -8321,7 +8345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>399</v>
       </c>
@@ -8377,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>399</v>
       </c>
@@ -8433,7 +8457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>399</v>
       </c>
@@ -8489,7 +8513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:18">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>399</v>
       </c>
@@ -8545,7 +8569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:18">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>399</v>
       </c>
@@ -8601,7 +8625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:18">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>399</v>
       </c>
@@ -8657,7 +8681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>399</v>
       </c>
@@ -8713,7 +8737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:18">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>399</v>
       </c>
@@ -8769,7 +8793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:18">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>399</v>
       </c>
@@ -8825,7 +8849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:18">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>399</v>
       </c>
@@ -8881,7 +8905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:18">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>399</v>
       </c>
@@ -8937,7 +8961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:18">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>399</v>
       </c>
@@ -8993,7 +9017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:18">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>399</v>
       </c>
@@ -9049,7 +9073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>399</v>
       </c>
@@ -9105,7 +9129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:18">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>399</v>
       </c>
@@ -9161,7 +9185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:18">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>399</v>
       </c>
@@ -9217,7 +9241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:18">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>399</v>
       </c>
@@ -9273,7 +9297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:18">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>399</v>
       </c>
@@ -9329,7 +9353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:18">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>399</v>
       </c>
@@ -9385,7 +9409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:18">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>399</v>
       </c>
@@ -9441,7 +9465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:18">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>399</v>
       </c>
@@ -9497,7 +9521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>399</v>
       </c>
@@ -9553,7 +9577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>399</v>
       </c>
@@ -9609,7 +9633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>399</v>
       </c>
@@ -9665,7 +9689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>399</v>
       </c>
@@ -9721,7 +9745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:18">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>399</v>
       </c>
@@ -9777,7 +9801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>399</v>
       </c>
@@ -9833,7 +9857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>399</v>
       </c>
@@ -9889,7 +9913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>399</v>
       </c>
@@ -9945,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>399</v>
       </c>
@@ -10001,7 +10025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>399</v>
       </c>
@@ -10057,7 +10081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:18">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>399</v>
       </c>
@@ -10113,7 +10137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>399</v>
       </c>
@@ -10169,7 +10193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>399</v>
       </c>
@@ -10225,7 +10249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>399</v>
       </c>
@@ -10281,7 +10305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>399</v>
       </c>
@@ -10337,7 +10361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>399</v>
       </c>
@@ -10393,7 +10417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>399</v>
       </c>
@@ -10449,7 +10473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>399</v>
       </c>
@@ -10505,7 +10529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>499</v>
       </c>
@@ -10561,7 +10585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>499</v>
       </c>
@@ -10617,7 +10641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>499</v>
       </c>
@@ -10673,7 +10697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:18">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>499</v>
       </c>
@@ -10729,7 +10753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>499</v>
       </c>
@@ -10785,7 +10809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:18">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>499</v>
       </c>
@@ -10841,7 +10865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>499</v>
       </c>
@@ -10897,7 +10921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>499</v>
       </c>
@@ -10953,7 +10977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>499</v>
       </c>
@@ -11009,7 +11033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:18">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>499</v>
       </c>
@@ -11065,7 +11089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>499</v>
       </c>
@@ -11121,7 +11145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>499</v>
       </c>
@@ -11177,7 +11201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>499</v>
       </c>
@@ -11233,7 +11257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:18">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>499</v>
       </c>
@@ -11289,7 +11313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:18">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>499</v>
       </c>
@@ -11345,7 +11369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:18">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>499</v>
       </c>
@@ -11401,7 +11425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:18">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>499</v>
       </c>
@@ -11457,7 +11481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:18">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>499</v>
       </c>
@@ -11513,7 +11537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:18">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>499</v>
       </c>
@@ -11569,7 +11593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:18">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>499</v>
       </c>
@@ -11625,7 +11649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:18">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>499</v>
       </c>
@@ -11681,7 +11705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:18">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>499</v>
       </c>
@@ -11737,7 +11761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:18">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>499</v>
       </c>
@@ -11793,7 +11817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:18">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>499</v>
       </c>
@@ -11849,7 +11873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:18">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>499</v>
       </c>
@@ -11905,7 +11929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:18">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>499</v>
       </c>
@@ -11961,7 +11985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:18">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>549</v>
       </c>
@@ -12017,7 +12041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:18">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>549</v>
       </c>
@@ -12073,7 +12097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:18">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>549</v>
       </c>
@@ -12129,7 +12153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>549</v>
       </c>
@@ -12185,7 +12209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:18">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>549</v>
       </c>
@@ -12241,7 +12265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:18">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>549</v>
       </c>
@@ -12297,7 +12321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:18">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>549</v>
       </c>
@@ -12353,7 +12377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:18">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>549</v>
       </c>
@@ -12409,7 +12433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:18">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>549</v>
       </c>
@@ -12465,7 +12489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:18">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>549</v>
       </c>
@@ -12521,7 +12545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:18">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>549</v>
       </c>
@@ -12577,7 +12601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:18">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>549</v>
       </c>
@@ -12633,7 +12657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>549</v>
       </c>
@@ -12689,7 +12713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:18">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>549</v>
       </c>
@@ -12745,7 +12769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>549</v>
       </c>
@@ -12801,7 +12825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:18">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>549</v>
       </c>
@@ -12857,7 +12881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:18">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>549</v>
       </c>
@@ -12913,7 +12937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:18">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>549</v>
       </c>
@@ -12969,7 +12993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:18">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>549</v>
       </c>
@@ -13025,7 +13049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:18">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>549</v>
       </c>
@@ -13081,7 +13105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:18">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>549</v>
       </c>
@@ -13137,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:18">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>549</v>
       </c>
@@ -13193,7 +13217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:18">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>549</v>
       </c>
@@ -13249,7 +13273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:18">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>549</v>
       </c>
@@ -13305,7 +13329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:18">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>549</v>
       </c>
@@ -13361,7 +13385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:18">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>549</v>
       </c>
@@ -13417,7 +13441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:18">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>549</v>
       </c>
@@ -13473,7 +13497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:18">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>599</v>
       </c>
@@ -13529,7 +13553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:18">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>599</v>
       </c>
@@ -13585,7 +13609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:18">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>599</v>
       </c>
@@ -13641,7 +13665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:18">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>599</v>
       </c>
@@ -13697,7 +13721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:18">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>599</v>
       </c>
@@ -13753,7 +13777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:18">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>599</v>
       </c>
@@ -13809,7 +13833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:18">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>599</v>
       </c>
@@ -13865,7 +13889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:18">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>599</v>
       </c>
@@ -13921,7 +13945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:18">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>599</v>
       </c>
@@ -13977,7 +14001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:18">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>599</v>
       </c>
@@ -14033,7 +14057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:18">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>599</v>
       </c>
@@ -14089,7 +14113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:18">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>599</v>
       </c>
@@ -14145,7 +14169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:18">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>599</v>
       </c>
@@ -14201,7 +14225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:18">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>599</v>
       </c>
@@ -14257,7 +14281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:18">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>599</v>
       </c>
@@ -14313,7 +14337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:18">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>599</v>
       </c>
@@ -14369,7 +14393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:18">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>599</v>
       </c>
@@ -14425,7 +14449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:18">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>599</v>
       </c>
@@ -14481,7 +14505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:18">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>599</v>
       </c>
@@ -14537,7 +14561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:18">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>599</v>
       </c>
@@ -14593,7 +14617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:18">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>599</v>
       </c>
@@ -14649,7 +14673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:18">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>599</v>
       </c>
@@ -14705,7 +14729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:18">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>599</v>
       </c>
@@ -14761,7 +14785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:18">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>599</v>
       </c>
@@ -14817,7 +14841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>599</v>
       </c>
@@ -14873,7 +14897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>599</v>
       </c>
@@ -14929,7 +14953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>599</v>
       </c>
@@ -14985,7 +15009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>599</v>
       </c>
@@ -15041,7 +15065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>599</v>
       </c>
@@ -15097,7 +15121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:18">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>599</v>
       </c>
@@ -15153,7 +15177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>599</v>
       </c>
@@ -15209,7 +15233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:18">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>599</v>
       </c>
@@ -15265,7 +15289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:18">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>599</v>
       </c>
@@ -15321,7 +15345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:18">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>599</v>
       </c>
@@ -15377,7 +15401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:18">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>599</v>
       </c>
@@ -15433,7 +15457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:18">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>599</v>
       </c>
@@ -15489,7 +15513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:18">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>599</v>
       </c>
@@ -15545,7 +15569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:18">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>599</v>
       </c>
@@ -15601,7 +15625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:18">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>599</v>
       </c>
@@ -15657,7 +15681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:18">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>599</v>
       </c>
@@ -15713,7 +15737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:18">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>599</v>
       </c>
@@ -15769,7 +15793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:18">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>599</v>
       </c>
@@ -15825,7 +15849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:18">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>599</v>
       </c>
@@ -15881,7 +15905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:18">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>599</v>
       </c>
@@ -15937,7 +15961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:18">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>599</v>
       </c>
@@ -15993,7 +16017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:18">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>599</v>
       </c>
@@ -16049,7 +16073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:18">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>599</v>
       </c>
@@ -16105,7 +16129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:18">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>599</v>
       </c>
@@ -16161,7 +16185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:18">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>599</v>
       </c>
@@ -16217,7 +16241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:18">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>599</v>
       </c>
@@ -16273,7 +16297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:18">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>599</v>
       </c>
@@ -16329,7 +16353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:18">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>599</v>
       </c>
@@ -16385,7 +16409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:18">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>599</v>
       </c>
@@ -16441,7 +16465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:18">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>599</v>
       </c>
@@ -16497,7 +16521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:18">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>599</v>
       </c>
@@ -16553,7 +16577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:18">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>599</v>
       </c>
@@ -16609,7 +16633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:18">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>599</v>
       </c>
@@ -16665,7 +16689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:18">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>599</v>
       </c>
@@ -16721,7 +16745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:18">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>599</v>
       </c>
@@ -16777,7 +16801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:18">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>599</v>
       </c>
@@ -16833,7 +16857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:18">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>599</v>
       </c>
@@ -16889,7 +16913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:18">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>599</v>
       </c>
@@ -16945,7 +16969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:18">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>599</v>
       </c>
@@ -17001,7 +17025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:18">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>599</v>
       </c>
@@ -17057,7 +17081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:18">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>599</v>
       </c>
@@ -17113,7 +17137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:18">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>599</v>
       </c>
@@ -17169,7 +17193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:18">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>599</v>
       </c>
@@ -17225,7 +17249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:18">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>599</v>
       </c>
@@ -17281,7 +17305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:18">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>599</v>
       </c>
@@ -17337,7 +17361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:18">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>599</v>
       </c>
@@ -17393,7 +17417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:18">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>599</v>
       </c>
@@ -17449,7 +17473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:18">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>599</v>
       </c>
@@ -17505,7 +17529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:18">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>599</v>
       </c>
@@ -17561,7 +17585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:18">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>599</v>
       </c>
@@ -17617,7 +17641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:18">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>599</v>
       </c>
@@ -17673,7 +17697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:18">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>599</v>
       </c>
@@ -17729,7 +17753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:18">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>599</v>
       </c>
@@ -17785,7 +17809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:18">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>599</v>
       </c>
@@ -17841,7 +17865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:18">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>599</v>
       </c>
@@ -17897,7 +17921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:18">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>599</v>
       </c>
@@ -17953,7 +17977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:18">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>599</v>
       </c>
@@ -18009,7 +18033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:18">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>599</v>
       </c>
@@ -18065,7 +18089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:18">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>599</v>
       </c>
@@ -18121,7 +18145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:18">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>599</v>
       </c>
@@ -18177,7 +18201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:18">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>599</v>
       </c>
@@ -18233,7 +18257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:18">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>599</v>
       </c>
@@ -18289,7 +18313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:18">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>699</v>
       </c>
@@ -18345,7 +18369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:18">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>699</v>
       </c>
@@ -18401,7 +18425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:18">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>699</v>
       </c>
@@ -18457,7 +18481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:18">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>699</v>
       </c>
@@ -18513,7 +18537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:18">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>699</v>
       </c>
@@ -18569,7 +18593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:18">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>699</v>
       </c>
@@ -18625,7 +18649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:18">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>699</v>
       </c>
@@ -18681,7 +18705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:18">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>699</v>
       </c>
@@ -18737,7 +18761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:18">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>699</v>
       </c>
@@ -18793,7 +18817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:18">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>699</v>
       </c>
@@ -18849,7 +18873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:18">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>699</v>
       </c>
@@ -18905,7 +18929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:18">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>699</v>
       </c>
@@ -18961,7 +18985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:18">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>699</v>
       </c>
@@ -19017,7 +19041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:18">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>699</v>
       </c>
@@ -19073,7 +19097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:18">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>699</v>
       </c>
@@ -19129,7 +19153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:18">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>699</v>
       </c>
@@ -19185,7 +19209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:18">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>699</v>
       </c>
@@ -19241,7 +19265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:18">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>699</v>
       </c>
@@ -19297,7 +19321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:18">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>699</v>
       </c>
@@ -19353,7 +19377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:18">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>699</v>
       </c>
@@ -19409,7 +19433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:18">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>699</v>
       </c>
@@ -19465,7 +19489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:18">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>699</v>
       </c>
@@ -19521,7 +19545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:18">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>699</v>
       </c>
@@ -19577,7 +19601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:18">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>699</v>
       </c>
@@ -19633,7 +19657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:18">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>699</v>
       </c>
@@ -19689,7 +19713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:18">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>699</v>
       </c>
@@ -19745,7 +19769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:18">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>699</v>
       </c>
@@ -19801,7 +19825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:18">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>699</v>
       </c>
@@ -19857,7 +19881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:18">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>699</v>
       </c>
@@ -19913,7 +19937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:18">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>699</v>
       </c>
@@ -19969,7 +19993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:18">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>699</v>
       </c>
@@ -20025,7 +20049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:18">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>699</v>
       </c>
@@ -20081,7 +20105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:18">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>699</v>
       </c>
@@ -20137,7 +20161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:18">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>699</v>
       </c>
@@ -20193,7 +20217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:18">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>699</v>
       </c>
@@ -20249,7 +20273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:18">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>699</v>
       </c>
@@ -20305,7 +20329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:18">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>699</v>
       </c>
@@ -20361,7 +20385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:18">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>699</v>
       </c>
@@ -20417,7 +20441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:18">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>699</v>
       </c>
@@ -20473,7 +20497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:18">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>699</v>
       </c>
@@ -20529,7 +20553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:18">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>699</v>
       </c>
@@ -20585,7 +20609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:18">
+    <row r="360" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>699</v>
       </c>
@@ -20641,7 +20665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:18">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>699</v>
       </c>
@@ -20697,7 +20721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:18">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>699</v>
       </c>
@@ -20753,7 +20777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:18">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>699</v>
       </c>
@@ -20809,7 +20833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:18">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>699</v>
       </c>
@@ -20865,7 +20889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:18">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>699</v>
       </c>
@@ -20921,7 +20945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:18">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>699</v>
       </c>
@@ -20977,7 +21001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:18">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>699</v>
       </c>
@@ -21033,7 +21057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:18">
+    <row r="368" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>699</v>
       </c>
@@ -21089,7 +21113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:18">
+    <row r="369" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>699</v>
       </c>
@@ -21145,7 +21169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:18">
+    <row r="370" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>699</v>
       </c>
@@ -21201,7 +21225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:18">
+    <row r="371" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>699</v>
       </c>
@@ -21257,7 +21281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:18">
+    <row r="372" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>699</v>
       </c>
@@ -21313,7 +21337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:18">
+    <row r="373" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>799</v>
       </c>
@@ -21369,7 +21393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:18">
+    <row r="374" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>799</v>
       </c>
@@ -21425,7 +21449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:18">
+    <row r="375" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>799</v>
       </c>
@@ -21481,7 +21505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:18">
+    <row r="376" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>799</v>
       </c>
@@ -21537,7 +21561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:18">
+    <row r="377" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>799</v>
       </c>
@@ -21593,7 +21617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:18">
+    <row r="378" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>799</v>
       </c>
@@ -21649,7 +21673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:18">
+    <row r="379" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>799</v>
       </c>
@@ -21705,7 +21729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:18">
+    <row r="380" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>799</v>
       </c>
@@ -21761,7 +21785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:18">
+    <row r="381" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>799</v>
       </c>
@@ -21817,7 +21841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:18">
+    <row r="382" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>799</v>
       </c>
@@ -21873,7 +21897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:18">
+    <row r="383" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>799</v>
       </c>
@@ -21929,7 +21953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:18">
+    <row r="384" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>799</v>
       </c>
@@ -21985,7 +22009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:18">
+    <row r="385" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>799</v>
       </c>
@@ -22041,7 +22065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:18">
+    <row r="386" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>799</v>
       </c>
@@ -22097,7 +22121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:18">
+    <row r="387" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>799</v>
       </c>
@@ -22153,7 +22177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:18">
+    <row r="388" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>799</v>
       </c>
@@ -22209,7 +22233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:18">
+    <row r="389" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>799</v>
       </c>
@@ -22265,7 +22289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:18">
+    <row r="390" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>799</v>
       </c>
@@ -22321,7 +22345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:18">
+    <row r="391" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>799</v>
       </c>
@@ -22377,7 +22401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:18">
+    <row r="392" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>799</v>
       </c>
@@ -22433,7 +22457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:18">
+    <row r="393" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>799</v>
       </c>
@@ -22489,7 +22513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:18">
+    <row r="394" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>799</v>
       </c>
@@ -22545,7 +22569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:18">
+    <row r="395" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>799</v>
       </c>
@@ -22601,7 +22625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:18">
+    <row r="396" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>799</v>
       </c>
@@ -22657,7 +22681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:18">
+    <row r="397" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>799</v>
       </c>
@@ -22713,7 +22737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:18">
+    <row r="398" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>799</v>
       </c>
@@ -22769,7 +22793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:18">
+    <row r="399" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>799</v>
       </c>
@@ -22825,7 +22849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:18">
+    <row r="400" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>799</v>
       </c>
@@ -22881,7 +22905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:18">
+    <row r="401" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>799</v>
       </c>
@@ -22937,7 +22961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:18">
+    <row r="402" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>799</v>
       </c>
@@ -22993,7 +23017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:18">
+    <row r="403" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>799</v>
       </c>
@@ -23049,7 +23073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:18">
+    <row r="404" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>799</v>
       </c>
@@ -23105,7 +23129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:18">
+    <row r="405" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>799</v>
       </c>
@@ -23161,7 +23185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:18">
+    <row r="406" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>799</v>
       </c>
@@ -23217,7 +23241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:18">
+    <row r="407" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>799</v>
       </c>
@@ -23273,7 +23297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:18">
+    <row r="408" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>799</v>
       </c>
@@ -23329,7 +23353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:18">
+    <row r="409" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>799</v>
       </c>
@@ -23385,7 +23409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:18">
+    <row r="410" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>799</v>
       </c>
@@ -23441,7 +23465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:18">
+    <row r="411" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>799</v>
       </c>
@@ -23497,7 +23521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:18">
+    <row r="412" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>799</v>
       </c>
@@ -23553,7 +23577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:18">
+    <row r="413" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>799</v>
       </c>
@@ -23609,7 +23633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:18">
+    <row r="414" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>799</v>
       </c>
@@ -23665,7 +23689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:18">
+    <row r="415" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>799</v>
       </c>
@@ -23721,7 +23745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:18">
+    <row r="416" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>799</v>
       </c>
@@ -23777,7 +23801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:18">
+    <row r="417" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>799</v>
       </c>
@@ -23833,7 +23857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:18">
+    <row r="418" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>799</v>
       </c>
@@ -23889,7 +23913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:18">
+    <row r="419" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>799</v>
       </c>
@@ -23945,7 +23969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:18">
+    <row r="420" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>799</v>
       </c>
@@ -24001,7 +24025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:18">
+    <row r="421" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>799</v>
       </c>
@@ -24057,7 +24081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:18">
+    <row r="422" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>799</v>
       </c>
@@ -24113,7 +24137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:18">
+    <row r="423" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>799</v>
       </c>
@@ -24169,7 +24193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:18">
+    <row r="424" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>799</v>
       </c>
@@ -24225,7 +24249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:18">
+    <row r="425" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>799</v>
       </c>
@@ -24281,7 +24305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:18">
+    <row r="426" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>799</v>
       </c>
@@ -24337,7 +24361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:18">
+    <row r="427" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>799</v>
       </c>
@@ -24393,7 +24417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:18">
+    <row r="428" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>799</v>
       </c>
@@ -24449,7 +24473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:18">
+    <row r="429" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>799</v>
       </c>
@@ -24505,7 +24529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:18">
+    <row r="430" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>799</v>
       </c>
@@ -24561,7 +24585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:18">
+    <row r="431" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>799</v>
       </c>
@@ -24617,7 +24641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:18">
+    <row r="432" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>799</v>
       </c>
@@ -24673,7 +24697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:18">
+    <row r="433" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>799</v>
       </c>
@@ -24729,7 +24753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:18">
+    <row r="434" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>799</v>
       </c>
@@ -24785,7 +24809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:18">
+    <row r="435" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>799</v>
       </c>
@@ -24841,7 +24865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:18">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>799</v>
       </c>
@@ -24897,7 +24921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:18">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>799</v>
       </c>
@@ -24953,7 +24977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:18">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>799</v>
       </c>
@@ -25009,7 +25033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:18">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>799</v>
       </c>
@@ -25065,7 +25089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:18">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>799</v>
       </c>
@@ -25121,7 +25145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:18">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>799</v>
       </c>
@@ -25177,7 +25201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:18">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>799</v>
       </c>
@@ -25233,7 +25257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:18">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>799</v>
       </c>
@@ -25289,7 +25313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:18">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>799</v>
       </c>
@@ -25345,7 +25369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:18">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>799</v>
       </c>
@@ -25401,7 +25425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:18">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>899</v>
       </c>
@@ -25457,7 +25481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:18">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>899</v>
       </c>
@@ -25513,7 +25537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:18">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>899</v>
       </c>
@@ -25569,7 +25593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:18">
+    <row r="449" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>899</v>
       </c>
@@ -25625,7 +25649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:18">
+    <row r="450" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>899</v>
       </c>
@@ -25681,7 +25705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:18">
+    <row r="451" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>899</v>
       </c>
@@ -25737,7 +25761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:18">
+    <row r="452" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>899</v>
       </c>
@@ -25793,7 +25817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:18">
+    <row r="453" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>899</v>
       </c>
@@ -25849,7 +25873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:18">
+    <row r="454" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>899</v>
       </c>
@@ -25905,7 +25929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:18">
+    <row r="455" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>899</v>
       </c>
@@ -25961,7 +25985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:18">
+    <row r="456" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>899</v>
       </c>
@@ -26017,7 +26041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:18">
+    <row r="457" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>899</v>
       </c>
@@ -26073,7 +26097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:18">
+    <row r="458" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>899</v>
       </c>
@@ -26129,7 +26153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:18">
+    <row r="459" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>899</v>
       </c>
@@ -26185,7 +26209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:18">
+    <row r="460" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>899</v>
       </c>
@@ -26241,7 +26265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:18">
+    <row r="461" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>899</v>
       </c>
@@ -26297,7 +26321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:18">
+    <row r="462" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>899</v>
       </c>
@@ -26353,7 +26377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:18">
+    <row r="463" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>899</v>
       </c>
@@ -26409,7 +26433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:18">
+    <row r="464" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>899</v>
       </c>
@@ -26465,7 +26489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:18">
+    <row r="465" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>899</v>
       </c>
@@ -26521,7 +26545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:18">
+    <row r="466" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>899</v>
       </c>
@@ -26577,7 +26601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:18">
+    <row r="467" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>899</v>
       </c>
@@ -26633,7 +26657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:18">
+    <row r="468" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>899</v>
       </c>
@@ -26689,7 +26713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:18">
+    <row r="469" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>899</v>
       </c>
@@ -26745,7 +26769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:18">
+    <row r="470" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>899</v>
       </c>
@@ -26801,7 +26825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:18">
+    <row r="471" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>899</v>
       </c>
@@ -26857,7 +26881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:18">
+    <row r="472" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>899</v>
       </c>
@@ -26913,7 +26937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:18">
+    <row r="473" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>899</v>
       </c>
@@ -26969,7 +26993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:18">
+    <row r="474" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>899</v>
       </c>
@@ -27025,7 +27049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:18">
+    <row r="475" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>899</v>
       </c>
@@ -27081,7 +27105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:18">
+    <row r="476" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>899</v>
       </c>
@@ -27137,7 +27161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:18">
+    <row r="477" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>899</v>
       </c>
@@ -27193,7 +27217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:18">
+    <row r="478" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>899</v>
       </c>
@@ -27249,7 +27273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:18">
+    <row r="479" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>899</v>
       </c>
@@ -27305,7 +27329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:18">
+    <row r="480" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>899</v>
       </c>
@@ -27361,7 +27385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:18">
+    <row r="481" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>899</v>
       </c>
@@ -27417,7 +27441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:18">
+    <row r="482" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>899</v>
       </c>
@@ -27473,7 +27497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:18">
+    <row r="483" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>899</v>
       </c>
@@ -27529,7 +27553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:18">
+    <row r="484" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>899</v>
       </c>
@@ -27585,7 +27609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:18">
+    <row r="485" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>899</v>
       </c>
@@ -27641,7 +27665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:18">
+    <row r="486" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>899</v>
       </c>
@@ -27697,7 +27721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:18">
+    <row r="487" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>899</v>
       </c>
@@ -27753,7 +27777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:18">
+    <row r="488" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>899</v>
       </c>
@@ -27809,7 +27833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:18">
+    <row r="489" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>899</v>
       </c>
@@ -27865,7 +27889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:18">
+    <row r="490" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>899</v>
       </c>
@@ -27921,7 +27945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:18">
+    <row r="491" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>899</v>
       </c>
@@ -27977,7 +28001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:18">
+    <row r="492" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>899</v>
       </c>
@@ -28033,7 +28057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:18">
+    <row r="493" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>899</v>
       </c>
@@ -28089,7 +28113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:18">
+    <row r="494" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>899</v>
       </c>
@@ -28145,7 +28169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:18">
+    <row r="495" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>899</v>
       </c>
@@ -28201,7 +28225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:18">
+    <row r="496" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>899</v>
       </c>
@@ -28257,7 +28281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:18">
+    <row r="497" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>899</v>
       </c>
@@ -28313,7 +28337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:18">
+    <row r="498" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>899</v>
       </c>
@@ -28369,7 +28393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:18">
+    <row r="499" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>899</v>
       </c>
@@ -28425,7 +28449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:18">
+    <row r="500" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>899</v>
       </c>
@@ -28481,7 +28505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:18">
+    <row r="501" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>899</v>
       </c>
@@ -28537,7 +28561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:18">
+    <row r="502" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>899</v>
       </c>
@@ -28593,7 +28617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:18">
+    <row r="503" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>899</v>
       </c>
@@ -28649,7 +28673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:18">
+    <row r="504" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>899</v>
       </c>
@@ -28705,7 +28729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:18">
+    <row r="505" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>899</v>
       </c>
@@ -28761,7 +28785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:18">
+    <row r="506" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>899</v>
       </c>
@@ -28817,7 +28841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:18">
+    <row r="507" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>899</v>
       </c>
@@ -28873,7 +28897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:18">
+    <row r="508" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>899</v>
       </c>
@@ -28929,7 +28953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:18">
+    <row r="509" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>899</v>
       </c>
@@ -28985,7 +29009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:18">
+    <row r="510" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>899</v>
       </c>
@@ -29041,7 +29065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:18">
+    <row r="511" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>899</v>
       </c>
@@ -29097,7 +29121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:18">
+    <row r="512" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>899</v>
       </c>
@@ -29153,7 +29177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:18">
+    <row r="513" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>899</v>
       </c>
@@ -29209,7 +29233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:18">
+    <row r="514" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>899</v>
       </c>
@@ -29265,7 +29289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:18">
+    <row r="515" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>899</v>
       </c>
@@ -29321,7 +29345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:18">
+    <row r="516" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>899</v>
       </c>
@@ -29377,7 +29401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:18">
+    <row r="517" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>899</v>
       </c>
@@ -29433,7 +29457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:18">
+    <row r="518" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>899</v>
       </c>
@@ -29489,7 +29513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:18">
+    <row r="519" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>899</v>
       </c>
@@ -29545,7 +29569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:18">
+    <row r="520" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>899</v>
       </c>
@@ -29601,7 +29625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:18">
+    <row r="521" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>899</v>
       </c>
@@ -29657,7 +29681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:18">
+    <row r="522" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>899</v>
       </c>
@@ -29713,7 +29737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:18">
+    <row r="523" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>899</v>
       </c>
@@ -29769,7 +29793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:18">
+    <row r="524" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>899</v>
       </c>
@@ -29825,7 +29849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:18">
+    <row r="525" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>899</v>
       </c>
@@ -29881,7 +29905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:18">
+    <row r="526" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>899</v>
       </c>
@@ -29937,7 +29961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:18">
+    <row r="527" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>899</v>
       </c>
@@ -29993,7 +30017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:18">
+    <row r="528" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>899</v>
       </c>
@@ -30049,7 +30073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:18">
+    <row r="529" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>899</v>
       </c>
@@ -30105,7 +30129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:18">
+    <row r="530" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>899</v>
       </c>
@@ -30161,7 +30185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:18">
+    <row r="531" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>899</v>
       </c>
@@ -30217,7 +30241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:18">
+    <row r="532" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>899</v>
       </c>
@@ -30273,7 +30297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:18">
+    <row r="533" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>899</v>
       </c>
@@ -30329,7 +30353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:18">
+    <row r="534" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>899</v>
       </c>
@@ -30385,7 +30409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:18">
+    <row r="535" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>899</v>
       </c>
@@ -30441,7 +30465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:18">
+    <row r="536" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>899</v>
       </c>
@@ -30497,7 +30521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:18">
+    <row r="537" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>899</v>
       </c>
@@ -30553,7 +30577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:18">
+    <row r="538" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>899</v>
       </c>
@@ -30609,7 +30633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:18">
+    <row r="539" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>899</v>
       </c>
@@ -30665,7 +30689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:18">
+    <row r="540" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>899</v>
       </c>
@@ -30721,7 +30745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:18">
+    <row r="541" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>899</v>
       </c>
@@ -30777,7 +30801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:18">
+    <row r="542" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>899</v>
       </c>
@@ -30833,7 +30857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:18">
+    <row r="543" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>899</v>
       </c>
@@ -30889,7 +30913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:18">
+    <row r="544" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>899</v>
       </c>
@@ -30945,7 +30969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:18">
+    <row r="545" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>899</v>
       </c>
@@ -31001,7 +31025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:18">
+    <row r="546" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>899</v>
       </c>
@@ -31057,7 +31081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:18">
+    <row r="547" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>999</v>
       </c>
@@ -31113,7 +31137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:18">
+    <row r="548" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>999</v>
       </c>
@@ -31169,7 +31193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:18">
+    <row r="549" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>999</v>
       </c>
@@ -31225,7 +31249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:18">
+    <row r="550" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>999</v>
       </c>
@@ -31281,7 +31305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:18">
+    <row r="551" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>999</v>
       </c>
@@ -31337,7 +31361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:18">
+    <row r="552" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>999</v>
       </c>
@@ -31393,7 +31417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:18">
+    <row r="553" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>999</v>
       </c>
@@ -31449,7 +31473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:18">
+    <row r="554" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>999</v>
       </c>
@@ -31505,7 +31529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:18">
+    <row r="555" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>999</v>
       </c>
@@ -31561,7 +31585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:18">
+    <row r="556" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>999</v>
       </c>
@@ -31617,7 +31641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:18">
+    <row r="557" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>999</v>
       </c>
@@ -31673,7 +31697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:18">
+    <row r="558" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>999</v>
       </c>
@@ -31729,7 +31753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:18">
+    <row r="559" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>999</v>
       </c>
@@ -31785,7 +31809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:18">
+    <row r="560" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>999</v>
       </c>
@@ -31841,7 +31865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:18">
+    <row r="561" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>999</v>
       </c>
@@ -31897,7 +31921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:18">
+    <row r="562" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>999</v>
       </c>
@@ -31953,7 +31977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:18">
+    <row r="563" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>999</v>
       </c>
@@ -32009,7 +32033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:18">
+    <row r="564" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>999</v>
       </c>
@@ -32065,7 +32089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:18">
+    <row r="565" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>999</v>
       </c>
@@ -32121,7 +32145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:18">
+    <row r="566" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>999</v>
       </c>
@@ -32177,7 +32201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:18">
+    <row r="567" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>999</v>
       </c>
@@ -32233,7 +32257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:18">
+    <row r="568" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>999</v>
       </c>
@@ -32289,7 +32313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:18">
+    <row r="569" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>999</v>
       </c>
@@ -32345,7 +32369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:18">
+    <row r="570" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>999</v>
       </c>
@@ -32401,7 +32425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:18">
+    <row r="571" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>999</v>
       </c>
@@ -32457,7 +32481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:18">
+    <row r="572" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>999</v>
       </c>
@@ -32513,7 +32537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:18">
+    <row r="573" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>999</v>
       </c>
@@ -32569,7 +32593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:18">
+    <row r="574" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>999</v>
       </c>
@@ -32625,7 +32649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:18">
+    <row r="575" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>999</v>
       </c>
@@ -32681,7 +32705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:18">
+    <row r="576" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>999</v>
       </c>
@@ -32737,7 +32761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:18">
+    <row r="577" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>999</v>
       </c>
@@ -32793,7 +32817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:18">
+    <row r="578" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>999</v>
       </c>
@@ -32849,7 +32873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:18">
+    <row r="579" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>999</v>
       </c>
@@ -32905,7 +32929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:18">
+    <row r="580" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>999</v>
       </c>
@@ -32961,7 +32985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="581" spans="1:18">
+    <row r="581" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>999</v>
       </c>
@@ -33017,7 +33041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:18">
+    <row r="582" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>999</v>
       </c>
@@ -33073,7 +33097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:18">
+    <row r="583" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>999</v>
       </c>
@@ -33129,7 +33153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:18">
+    <row r="584" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>999</v>
       </c>
@@ -33185,7 +33209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:18">
+    <row r="585" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>999</v>
       </c>
@@ -33241,7 +33265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:18">
+    <row r="586" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>999</v>
       </c>
@@ -33297,7 +33321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:18">
+    <row r="587" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>999</v>
       </c>
@@ -33353,7 +33377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:18">
+    <row r="588" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>999</v>
       </c>
@@ -33409,7 +33433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:18">
+    <row r="589" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>999</v>
       </c>
@@ -33465,7 +33489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:18">
+    <row r="590" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>999</v>
       </c>
@@ -33521,7 +33545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:18">
+    <row r="591" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>999</v>
       </c>
@@ -33577,7 +33601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:18">
+    <row r="592" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>999</v>
       </c>
@@ -33633,7 +33657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:18">
+    <row r="593" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>999</v>
       </c>
@@ -33689,7 +33713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:18">
+    <row r="594" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>999</v>
       </c>
@@ -33745,7 +33769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:18">
+    <row r="595" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>999</v>
       </c>
@@ -33801,7 +33825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="596" spans="1:18">
+    <row r="596" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>999</v>
       </c>
@@ -33857,7 +33881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="1:18">
+    <row r="597" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>999</v>
       </c>
@@ -33913,7 +33937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="1:18">
+    <row r="598" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>999</v>
       </c>
@@ -33969,7 +33993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:18">
+    <row r="599" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>999</v>
       </c>
@@ -34025,7 +34049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:18">
+    <row r="600" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>999</v>
       </c>
@@ -34081,7 +34105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="601" spans="1:18">
+    <row r="601" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>999</v>
       </c>
@@ -34137,7 +34161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:18">
+    <row r="602" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>999</v>
       </c>
@@ -34193,7 +34217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:18">
+    <row r="603" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>999</v>
       </c>
@@ -34249,7 +34273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:18">
+    <row r="604" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>999</v>
       </c>
@@ -34305,7 +34329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:18">
+    <row r="605" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>999</v>
       </c>
@@ -34361,7 +34385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:18">
+    <row r="606" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>999</v>
       </c>
@@ -34417,7 +34441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:18">
+    <row r="607" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>999</v>
       </c>
@@ -34473,7 +34497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:18">
+    <row r="608" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>999</v>
       </c>
@@ -34529,7 +34553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:18">
+    <row r="609" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>999</v>
       </c>
@@ -34585,7 +34609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:18">
+    <row r="610" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>999</v>
       </c>
@@ -34641,7 +34665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:18">
+    <row r="611" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>999</v>
       </c>
@@ -34697,7 +34721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:18">
+    <row r="612" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>999</v>
       </c>
@@ -34753,7 +34777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:18">
+    <row r="613" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>999</v>
       </c>
@@ -34809,7 +34833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:18">
+    <row r="614" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>999</v>
       </c>
@@ -34865,7 +34889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:18">
+    <row r="615" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>999</v>
       </c>
@@ -34921,7 +34945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:18">
+    <row r="616" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>999</v>
       </c>
@@ -34977,7 +35001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:18">
+    <row r="617" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>999</v>
       </c>
@@ -35033,7 +35057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:18">
+    <row r="618" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>999</v>
       </c>
@@ -35089,7 +35113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:18">
+    <row r="619" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>999</v>
       </c>
@@ -35145,7 +35169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:18">
+    <row r="620" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>999</v>
       </c>
@@ -35201,7 +35225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="621" spans="1:18">
+    <row r="621" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>999</v>
       </c>
@@ -35257,7 +35281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:18">
+    <row r="622" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>999</v>
       </c>
@@ -35313,7 +35337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:18">
+    <row r="623" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>999</v>
       </c>
@@ -35369,7 +35393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:18">
+    <row r="624" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>999</v>
       </c>
@@ -35425,7 +35449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:18">
+    <row r="625" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>999</v>
       </c>
@@ -35481,7 +35505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="1:18">
+    <row r="626" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>1199</v>
       </c>
@@ -35537,7 +35561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:18">
+    <row r="627" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>1199</v>
       </c>
@@ -35593,7 +35617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="1:18">
+    <row r="628" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>1199</v>
       </c>
@@ -35649,7 +35673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:18">
+    <row r="629" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>1199</v>
       </c>
@@ -35705,7 +35729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:18">
+    <row r="630" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>1199</v>
       </c>
@@ -35761,7 +35785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:18">
+    <row r="631" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>1199</v>
       </c>
@@ -35817,7 +35841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="1:18">
+    <row r="632" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>1199</v>
       </c>
@@ -35873,7 +35897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="1:18">
+    <row r="633" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>1199</v>
       </c>
@@ -35929,7 +35953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:18">
+    <row r="634" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>1199</v>
       </c>
@@ -35985,7 +36009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:18">
+    <row r="635" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>1199</v>
       </c>
@@ -36041,7 +36065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:18">
+    <row r="636" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>1199</v>
       </c>
@@ -36097,7 +36121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="637" spans="1:18">
+    <row r="637" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>1199</v>
       </c>
@@ -36153,7 +36177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="1:18">
+    <row r="638" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>1199</v>
       </c>
@@ -36209,7 +36233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:18">
+    <row r="639" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>1199</v>
       </c>
@@ -36265,7 +36289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="640" spans="1:18">
+    <row r="640" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>1199</v>
       </c>
@@ -36321,7 +36345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:18">
+    <row r="641" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>1199</v>
       </c>
@@ -36377,7 +36401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:18">
+    <row r="642" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>1199</v>
       </c>
@@ -36433,7 +36457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:18">
+    <row r="643" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>1199</v>
       </c>
@@ -36489,7 +36513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:18">
+    <row r="644" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>1199</v>
       </c>
@@ -36545,7 +36569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:18">
+    <row r="645" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>1199</v>
       </c>
@@ -36601,7 +36625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:18">
+    <row r="646" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>1199</v>
       </c>
@@ -36657,7 +36681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="647" spans="1:18">
+    <row r="647" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>1199</v>
       </c>
@@ -36713,7 +36737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="1:18">
+    <row r="648" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>1199</v>
       </c>
@@ -36769,7 +36793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:18">
+    <row r="649" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>1199</v>
       </c>
@@ -36825,7 +36849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="650" spans="1:18">
+    <row r="650" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>1199</v>
       </c>
@@ -36881,7 +36905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:18">
+    <row r="651" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>1199</v>
       </c>
@@ -36937,7 +36961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:18">
+    <row r="652" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>1199</v>
       </c>
@@ -36993,7 +37017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="653" spans="1:18">
+    <row r="653" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>1199</v>
       </c>
@@ -37049,7 +37073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:18">
+    <row r="654" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>1199</v>
       </c>
@@ -37105,7 +37129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:18">
+    <row r="655" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>1199</v>
       </c>
@@ -37161,7 +37185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:18">
+    <row r="656" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>1199</v>
       </c>
@@ -37217,7 +37241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:18">
+    <row r="657" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>1199</v>
       </c>
@@ -37273,7 +37297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="658" spans="1:18">
+    <row r="658" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>1199</v>
       </c>
@@ -37329,7 +37353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="659" spans="1:18">
+    <row r="659" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>1199</v>
       </c>
@@ -37385,7 +37409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="660" spans="1:18">
+    <row r="660" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>1199</v>
       </c>
@@ -37441,7 +37465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:18">
+    <row r="661" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>1199</v>
       </c>
@@ -37497,7 +37521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:18">
+    <row r="662" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>1199</v>
       </c>
@@ -37553,7 +37577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:18">
+    <row r="663" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>1199</v>
       </c>
@@ -37609,7 +37633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="664" spans="1:18">
+    <row r="664" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>1199</v>
       </c>
@@ -37665,7 +37689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="665" spans="1:18">
+    <row r="665" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>1199</v>
       </c>
@@ -37721,7 +37745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="1:18">
+    <row r="666" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>1199</v>
       </c>
@@ -37777,7 +37801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:18">
+    <row r="667" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>1199</v>
       </c>
@@ -37833,7 +37857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:18">
+    <row r="668" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>1199</v>
       </c>
@@ -37889,7 +37913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:18">
+    <row r="669" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>1199</v>
       </c>
@@ -37945,7 +37969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="670" spans="1:18">
+    <row r="670" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>1199</v>
       </c>
@@ -38001,7 +38025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:18">
+    <row r="671" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>1199</v>
       </c>
@@ -38057,7 +38081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="672" spans="1:18">
+    <row r="672" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>1199</v>
       </c>
@@ -38113,7 +38137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="673" spans="1:18">
+    <row r="673" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>1199</v>
       </c>
@@ -38169,7 +38193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="674" spans="1:18">
+    <row r="674" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>1199</v>
       </c>
@@ -38225,7 +38249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:18">
+    <row r="675" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>1199</v>
       </c>
@@ -38281,7 +38305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:18">
+    <row r="676" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>1199</v>
       </c>
@@ -38337,7 +38361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:18">
+    <row r="677" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>1199</v>
       </c>
@@ -38393,7 +38417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:18">
+    <row r="678" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>1199</v>
       </c>
@@ -38449,7 +38473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="1:18">
+    <row r="679" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>1199</v>
       </c>
@@ -38505,7 +38529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:18">
+    <row r="680" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>1199</v>
       </c>
@@ -38561,7 +38585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:18">
+    <row r="681" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>1199</v>
       </c>
@@ -38617,7 +38641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="682" spans="1:18">
+    <row r="682" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>1199</v>
       </c>
@@ -38673,7 +38697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:18">
+    <row r="683" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>1199</v>
       </c>
@@ -38729,7 +38753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="684" spans="1:18">
+    <row r="684" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>1199</v>
       </c>
@@ -38785,7 +38809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="685" spans="1:18">
+    <row r="685" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>1199</v>
       </c>
@@ -38841,7 +38865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="686" spans="1:18">
+    <row r="686" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>1199</v>
       </c>
@@ -38897,7 +38921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="687" spans="1:18">
+    <row r="687" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>1199</v>
       </c>
@@ -38953,7 +38977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="1:18">
+    <row r="688" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>1199</v>
       </c>
@@ -39009,7 +39033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:18">
+    <row r="689" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>1199</v>
       </c>
@@ -39065,7 +39089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="690" spans="1:18">
+    <row r="690" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>1199</v>
       </c>
@@ -39121,7 +39145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="691" spans="1:18">
+    <row r="691" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>1199</v>
       </c>
@@ -39177,7 +39201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:18">
+    <row r="692" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>1199</v>
       </c>
@@ -39233,7 +39257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:18">
+    <row r="693" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>1199</v>
       </c>
@@ -39289,7 +39313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:18">
+    <row r="694" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>1199</v>
       </c>
@@ -39345,7 +39369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:18">
+    <row r="695" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>1199</v>
       </c>
@@ -39401,7 +39425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:18">
+    <row r="696" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>1199</v>
       </c>
@@ -39457,7 +39481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:18">
+    <row r="697" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>1199</v>
       </c>
@@ -39513,7 +39537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="1:18">
+    <row r="698" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>1199</v>
       </c>
@@ -39575,6 +39599,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DED2A91AA173094FA81FCEDD6E3E30A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b5493765fa246dc221950d2373830c73">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77439b7f-2d32-491e-906d-de495e876e17" xmlns:ns3="bc752ab6-5a34-4bbb-a36d-488c397d8a23" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bf03130b60c02e26a9cc380515a00585" ns2:_="" ns3:_="">
     <xsd:import namespace="77439b7f-2d32-491e-906d-de495e876e17"/>
@@ -39781,15 +39814,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -39802,13 +39826,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C307AC98-0354-4466-8F53-5F754A7ED30A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E5B4861-F368-4872-A780-836EBC3E16CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E5B4861-F368-4872-A780-836EBC3E16CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C307AC98-0354-4466-8F53-5F754A7ED30A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77439b7f-2d32-491e-906d-de495e876e17"/>
+    <ds:schemaRef ds:uri="bc752ab6-5a34-4bbb-a36d-488c397d8a23"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5D51ED4-B22A-4442-AA72-4A73BA27FE8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5D51ED4-B22A-4442-AA72-4A73BA27FE8E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="77439b7f-2d32-491e-906d-de495e876e17"/>
+    <ds:schemaRef ds:uri="bc752ab6-5a34-4bbb-a36d-488c397d8a23"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>